--- a/analisis_diseno_3_bti/lote_6/instrumentos/planilla_tiempos_encuentro_35.xlsx
+++ b/analisis_diseno_3_bti/lote_6/instrumentos/planilla_tiempos_encuentro_35.xlsx
@@ -423,11 +423,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -582,11 +582,22 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>¿Los datos son válidos?</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>IF(AND(ISNUMBER(B4),INT(B4)=B4,B4&gt;=1,ISNUMBER(B5),INT(B5)=B5,B5&gt;=1,ISNUMBER(B6),INT(B6)=B6,B6&gt;=1,ISNUMBER(B7),INT(B7)=B7,B7&gt;=1,ISNUMBER(B8),INT(B8)=B8,B8&gt;=0,ISNUMBER(B9),INT(B9)=B9,B9&gt;=1,ISNUMBER(B10),INT(B10)=B10,B10&gt;=0,ISNUMBER(B11),INT(B11)=B11,B11&gt;=0),"Sí","No: revisá los datos (enteros; equipos, estudiantes, minutos de la HC, de la demostración y de la defensa, mayores que 0)")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -596,7 +607,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>B4*(B7+B8)</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",B4*(B7+B8))</f>
         <v/>
       </c>
     </row>
@@ -607,7 +618,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>B5*B9</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",B5*B9)</f>
         <v/>
       </c>
     </row>
@@ -618,7 +629,7 @@
         </is>
       </c>
       <c r="B16">
-        <f>B14+B15</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",B14+B15)</f>
         <v/>
       </c>
     </row>
@@ -629,7 +640,7 @@
         </is>
       </c>
       <c r="B17">
-        <f>5*B6</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",5*B6)</f>
         <v/>
       </c>
     </row>
@@ -640,120 +651,179 @@
         </is>
       </c>
       <c r="B18">
-        <f>B17-B16</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",B17-B16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Defensas que pasan al Encuentro 36</t>
+          <t>Minutos de demostración que no entran en el Encuentro 35</t>
         </is>
       </c>
       <c r="B19">
-        <f>IF(B18&lt;0,ROUNDUP(-B18/B9,0),0)</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",MAX(0,B14-B17))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Minutos de recuperaciones en el Encuentro 36</t>
+          <t>Defensas que pasan al Encuentro 36 (enteras)</t>
         </is>
       </c>
       <c r="B20">
-        <f>B10*B11</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",IF(B18&gt;=0,0,IF(B19&gt;0,B5,ROUNDUP(-B18/B9,0))))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Minutos de evaluación disponibles en el Encuentro 36 (3 HC)</t>
+          <t>Minutos trasladados al Encuentro 36 (defensas × minutos por defensa, más demostraciones)</t>
         </is>
       </c>
       <c r="B21">
-        <f>3*B6</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",B20*B9+B19)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Diferencia en el Encuentro 36 (negativo: no alcanza)</t>
+          <t>Minutos de recuperaciones en el Encuentro 36</t>
         </is>
       </c>
       <c r="B22">
-        <f>B21-B20-MAX(0,-B18)</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",B10*B11)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alternativa</t>
+          <t>Minutos de evaluación disponibles en el Encuentro 36 (3 HC)</t>
         </is>
       </c>
       <c r="B23">
-        <f>IF(B18&gt;=0,"A",IF(B22&gt;=0,"B","B + calendario institucional autorizado"))</f>
+        <f>IF($B$13&lt;&gt;"Sí","—",3*B6)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Diferencia en el Encuentro 36 (negativo: no alcanza)</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>IF($B$13&lt;&gt;"Sí","—",B23-B22-B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alternativa</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>IF($B$13&lt;&gt;"Sí","—",IF(B18&gt;=0,"A",IF(B24&gt;=0,"B","B + calendario institucional autorizado")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Minutos sin lugar (requieren tiempo institucional autorizado)</t>
         </is>
       </c>
-      <c r="B24">
-        <f>MAX(0,-B22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Alternativas</t>
-        </is>
+      <c r="B26">
+        <f>IF($B$13&lt;&gt;"Sí","—",MAX(0,-B24))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Aviso</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IF($B$13&lt;&gt;"Sí","—",IF(B19&gt;0,"Las demostraciones solas superan el Encuentro 35",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>A. Todo en el Encuentro 35</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Si la planilla da diferencia positiva o cero: demostraciones en plenario con tiempo fijo y, después, las defensas individuales una por una. Mientras el docente toma una defensa, el resto del curso completa su ficha de retrospectiva (preparación del Encuentro 36, sin evaluación). Un solo evaluador.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>B. Defensas que continúan en el Encuentro 36</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Si el Encuentro 35 no alcanza: las defensas que faltan se toman al comienzo de las 3 HC de evaluación del Encuentro 36, antes que las recuperaciones. Las recuperaciones se ordenan por prioridad (condición mínima, evidencia ausente, nivel Inicial) en el tiempo que queda. Ninguna evidencia obligatoria se elimina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Si el Encuentro 35 no alcanza: las defensas que faltan se toman al comienzo de las 3 HC de evaluación del Encuentro 36, antes que las recuperaciones; se cuentan por defensas enteras. Las recuperaciones se ordenan por prioridad (condición mínima, evidencia ausente, nivel Inicial) en el tiempo que queda. Ninguna evidencia obligatoria se elimina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>B+. Si tampoco alcanza el Encuentro 36</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Los minutos que la planilla da «sin lugar» se programan en el tiempo que la institución autorice dentro de su calendario, y se registran (qué estudiantes, qué evidencia, cuándo). No se suponen horas extraordinarias de docentes ni de estudiantes que la institución no haya dispuesto.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="8">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 0." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 0." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Escribí un número entero mayor o igual que 0." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>